--- a/attendance_ready.xlsx
+++ b/attendance_ready.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,358 +438,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>19:46</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>19:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>06:34</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>06:35</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>06:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>06:24</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>19:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>06:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>06:24</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>06:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>16:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>09:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>10:08</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/attendance_ready.xlsx
+++ b/attendance_ready.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,952 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>20:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>21:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>21:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>07:38</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>06:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>18:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
